--- a/All-IOPins.xlsx
+++ b/All-IOPins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sawtelles\Documents\GitHub\Teensy-Odd-and-Ends\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swsya\Documents\GitHub\Teensy-Odd-and-Ends\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF21DE72-E386-4CCE-B694-28AF3D079C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4467C36C-A2FC-496D-926E-0B1E2597C2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="18240" windowHeight="28320" xr2:uid="{207FC95A-C154-4EA4-B2D9-D2F6000D8F44}"/>
+    <workbookView xWindow="21432" yWindow="0" windowWidth="19476" windowHeight="16656" xr2:uid="{207FC95A-C154-4EA4-B2D9-D2F6000D8F44}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,36 +20,19 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="281">
   <si>
     <t>BIT</t>
   </si>
   <si>
-    <t xml:space="preserve"> 0</t>
-  </si>
-  <si>
     <t>AD_B0_03</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1</t>
-  </si>
-  <si>
     <t>AD_B0_02</t>
   </si>
   <si>
@@ -110,51 +93,27 @@
     <t>B0_03</t>
   </si>
   <si>
-    <t>14/A0</t>
-  </si>
-  <si>
     <t>AD_B1_02</t>
   </si>
   <si>
-    <t>15/A1</t>
-  </si>
-  <si>
     <t>AD_B1_03</t>
   </si>
   <si>
-    <t>16/A2</t>
-  </si>
-  <si>
     <t>AD_B1_07</t>
   </si>
   <si>
-    <t>17/A3</t>
-  </si>
-  <si>
     <t>AD_B1_06</t>
   </si>
   <si>
-    <t>18/A4</t>
-  </si>
-  <si>
     <t>AD_B1_01</t>
   </si>
   <si>
-    <t>19/A5</t>
-  </si>
-  <si>
     <t>AD_B1_00</t>
   </si>
   <si>
-    <t>20/A6</t>
-  </si>
-  <si>
     <t>AD_B1_10</t>
   </si>
   <si>
-    <t>21/A7</t>
-  </si>
-  <si>
     <t>AD_B1_11</t>
   </si>
   <si>
@@ -170,15 +129,9 @@
     <t>AD_B1_09</t>
   </si>
   <si>
-    <t>24/A10</t>
-  </si>
-  <si>
     <t>AD_B0_12</t>
   </si>
   <si>
-    <t>25/A11</t>
-  </si>
-  <si>
     <t>AD_B0_13</t>
   </si>
   <si>
@@ -230,15 +183,9 @@
     <t>EMC_07</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t xml:space="preserve">B1_13    </t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
     <t xml:space="preserve">B1_12    </t>
   </si>
   <si>
@@ -863,10 +810,64 @@
     <t>27</t>
   </si>
   <si>
-    <t xml:space="preserve">Shows where all processor I/O  pins and, if they connect on the T4.1, what pin/function they go to. </t>
-  </si>
-  <si>
     <t>NOTE: Although high numbered pins are assigned, Teensy compiler will not recognize pins above CORE_NUM_DIGITAL (55). So for example , pinMode(85, INPUT) will be ignored.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0-RX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1-TX1</t>
+  </si>
+  <si>
+    <t>7-RX2</t>
+  </si>
+  <si>
+    <t>8-TX2</t>
+  </si>
+  <si>
+    <t>24/A10-SCL2-TX6</t>
+  </si>
+  <si>
+    <t>25/A11-SDA2-RX6</t>
+  </si>
+  <si>
+    <t>28-RX7</t>
+  </si>
+  <si>
+    <t>29-TX7</t>
+  </si>
+  <si>
+    <t>35-TX8</t>
+  </si>
+  <si>
+    <t>34-RX8</t>
+  </si>
+  <si>
+    <t>14/A0-TX3</t>
+  </si>
+  <si>
+    <t>15/A1-RX3</t>
+  </si>
+  <si>
+    <t>20/A6-TX5</t>
+  </si>
+  <si>
+    <t>21/A7-RX5</t>
+  </si>
+  <si>
+    <t>18/A4-SDA</t>
+  </si>
+  <si>
+    <t>19/A5-SCL</t>
+  </si>
+  <si>
+    <t>17/A3-TX4-SDA1</t>
+  </si>
+  <si>
+    <t>16/A2-RX4-SCL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shows all processor I/O  pins and, if they connect on the T4.1, what pin/function they go to. </t>
   </si>
 </sst>
 </file>
@@ -969,7 +970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -989,9 +990,12 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1328,25 +1332,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9656BE50-9C77-4DF8-ABEC-98B97523EA1E}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="8.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.85546875" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="8.109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" customWidth="1"/>
+    <col min="11" max="11" width="6.88671875" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1359,9 +1363,9 @@
       <c r="J1" s="11"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -1374,1149 +1378,1149 @@
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
     </row>
-    <row r="3" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-    </row>
-    <row r="4" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+    </row>
+    <row r="4" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <f t="shared" ref="A7:A47" si="0">A6+1</f>
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="H9" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C12" s="2">
         <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="1" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>44</v>
+        <v>266</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>46</v>
+        <v>267</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="1" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="I19" s="1" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="6" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="K31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="2">
-        <v>8</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="2">
-        <v>7</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="1" t="s">
+    </row>
+    <row r="32" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="C32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E32" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="H28" s="2" t="s">
+      <c r="B33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="D33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="I33" s="1" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>64</v>
+        <v>271</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>54</v>
+        <v>269</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="5"/>
     </row>
-    <row r="37" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="1"/>
       <c r="C37" s="2"/>
       <c r="D37" s="1"/>
       <c r="E37" s="2"/>
       <c r="F37" s="7" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="2"/>
@@ -2524,7 +2528,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <f>A36+1</f>
         <v>32</v>
@@ -2534,19 +2538,19 @@
       <c r="D38" s="1"/>
       <c r="E38" s="2"/>
       <c r="F38" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>52</v>
+        <v>268</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2556,19 +2560,19 @@
       <c r="D39" s="1"/>
       <c r="E39" s="2"/>
       <c r="F39" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2578,19 +2582,19 @@
       <c r="D40" s="1"/>
       <c r="E40" s="2"/>
       <c r="F40" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2600,19 +2604,19 @@
       <c r="D41" s="1"/>
       <c r="E41" s="2"/>
       <c r="F41" s="1" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2622,19 +2626,19 @@
       <c r="D42" s="1"/>
       <c r="E42" s="2"/>
       <c r="F42" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2644,19 +2648,19 @@
       <c r="D43" s="1"/>
       <c r="E43" s="2"/>
       <c r="F43" s="1" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2666,19 +2670,19 @@
       <c r="D44" s="1"/>
       <c r="E44" s="2"/>
       <c r="F44" s="1" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2688,19 +2692,19 @@
       <c r="D45" s="1"/>
       <c r="E45" s="2"/>
       <c r="F45" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2710,19 +2714,19 @@
       <c r="D46" s="1"/>
       <c r="E46" s="2"/>
       <c r="F46" s="1" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2732,13 +2736,13 @@
       <c r="D47" s="1"/>
       <c r="E47" s="2"/>
       <c r="F47" s="1" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -2757,7 +2761,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C5:C8 E7:E8 G9:G13 C33:C34 C16 G38 G35:G36 G42:G43 C12 C18:C24" numberStoredAsText="1"/>
+    <ignoredError sqref="C5:C8 G9:G13 C16 G35 G42:G43 C12 C18:C20 C23:C24" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/All-IOPins.xlsx
+++ b/All-IOPins.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sawtelles\Documents\GitHub\Teensy-Odd-and-Ends\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF21DE72-E386-4CCE-B694-28AF3D079C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80172C5D-296E-42DC-8FB1-902F17EB3840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="18240" windowHeight="28320" xr2:uid="{207FC95A-C154-4EA4-B2D9-D2F6000D8F44}"/>
   </bookViews>
@@ -969,7 +969,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -989,9 +989,12 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1374,20 +1377,20 @@
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
     </row>
-    <row r="3" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
     </row>
     <row r="4" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">

--- a/All-IOPins.xlsx
+++ b/All-IOPins.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sawtelles\Documents\GitHub\Teensy-Odd-and-Ends\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80172C5D-296E-42DC-8FB1-902F17EB3840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71831CA7-D14D-44F9-9788-4C7B3732D427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="18240" windowHeight="28320" xr2:uid="{207FC95A-C154-4EA4-B2D9-D2F6000D8F44}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="281">
   <si>
     <t>BIT</t>
   </si>
@@ -701,9 +701,6 @@
     <t>81</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>80</t>
   </si>
   <si>
@@ -743,9 +740,6 @@
     <t>67</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>66</t>
   </si>
   <si>
@@ -797,76 +791,94 @@
     <t>91</t>
   </si>
   <si>
-    <t>bit</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
     <t xml:space="preserve">Shows where all processor I/O  pins and, if they connect on the T4.1, what pin/function they go to. </t>
   </si>
   <si>
     <t>NOTE: Although high numbered pins are assigned, Teensy compiler will not recognize pins above CORE_NUM_DIGITAL (55). So for example , pinMode(85, INPUT) will be ignored.</t>
+  </si>
+  <si>
+    <t>MISO</t>
+  </si>
+  <si>
+    <t>MOSI</t>
+  </si>
+  <si>
+    <t>SCK (LED)</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>TX2</t>
+  </si>
+  <si>
+    <t>RX2</t>
+  </si>
+  <si>
+    <t>TX8</t>
+  </si>
+  <si>
+    <t>RX8</t>
+  </si>
+  <si>
+    <t>RX7</t>
+  </si>
+  <si>
+    <t>TX7</t>
+  </si>
+  <si>
+    <t>CRX3</t>
+  </si>
+  <si>
+    <t>CTX3</t>
+  </si>
+  <si>
+    <t>TX3</t>
+  </si>
+  <si>
+    <t>RX3</t>
+  </si>
+  <si>
+    <t>TX5</t>
+  </si>
+  <si>
+    <t>RX5</t>
+  </si>
+  <si>
+    <t>SCL</t>
+  </si>
+  <si>
+    <t>SDA</t>
+  </si>
+  <si>
+    <t>TX4/SDA1</t>
+  </si>
+  <si>
+    <t>RX4/SCL1</t>
+  </si>
+  <si>
+    <t>TX6/SCL2</t>
+  </si>
+  <si>
+    <t>RX6/SDA2</t>
+  </si>
+  <si>
+    <t>FUNCTION(S)</t>
+  </si>
+  <si>
+    <t>ARDUINO PIN</t>
+  </si>
+  <si>
+    <t>SCK1</t>
+  </si>
+  <si>
+    <t>MOSI1</t>
+  </si>
+  <si>
+    <t>RX1/CS1</t>
+  </si>
+  <si>
+    <t>TX1/MISO1</t>
   </si>
 </sst>
 </file>
@@ -904,7 +916,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -943,19 +955,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -969,7 +968,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -979,21 +978,22 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1330,69 +1330,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9656BE50-9C77-4DF8-ABEC-98B97523EA1E}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
     <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="8.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.85546875" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15.28515625" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="8"/>
-    </row>
-    <row r="2" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-    </row>
-    <row r="3" spans="1:11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-    </row>
-    <row r="4" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="8"/>
+    </row>
+    <row r="2" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="9"/>
+    </row>
+    <row r="3" spans="1:15" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1400,34 +1415,46 @@
         <v>210</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -1438,31 +1465,36 @@
         <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1"/>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>1</v>
@@ -1474,31 +1506,38 @@
         <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6">
+        <f>H5+1</f>
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="K6" s="1"/>
+      <c r="L6">
+        <f>L5+1</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <f t="shared" ref="A7:A47" si="0">A6+1</f>
         <v>2</v>
@@ -1510,31 +1549,40 @@
         <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H7">
+        <f t="shared" ref="H7:H47" si="1">H6+1</f>
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7">
+        <f t="shared" ref="L7:L36" si="2">L6+1</f>
+        <v>2</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1546,31 +1594,40 @@
         <v>22</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1579,34 +1636,39 @@
         <v>144</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D9" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1"/>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="I9" s="1" t="s">
+      <c r="K9" s="1"/>
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1615,34 +1677,39 @@
         <v>145</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D10" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1"/>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="K10" s="1"/>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1651,30 +1718,37 @@
         <v>146</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D11" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1"/>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="I11" s="1" t="s">
+      <c r="K11" s="1"/>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1685,28 +1759,35 @@
       <c r="C12" s="2">
         <v>6</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1"/>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="I12" s="1" t="s">
+      <c r="K12" s="1"/>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="M12" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1717,28 +1798,35 @@
       <c r="C13" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1"/>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="1">
+      <c r="J13" s="1">
         <v>5</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="I13" s="1" t="s">
+      <c r="K13" s="1"/>
+      <c r="L13">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1749,28 +1837,35 @@
       <c r="C14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1"/>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1781,28 +1876,35 @@
       <c r="C15" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1"/>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1811,28 +1913,35 @@
         <v>15</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1843,28 +1952,37 @@
       <c r="C17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="L17">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="J17" s="1"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1873,28 +1991,37 @@
         <v>147</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J18" s="1"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1903,28 +2030,35 @@
         <v>148</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J19" s="1"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1933,28 +2067,36 @@
         <v>149</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="6"/>
+      <c r="E20" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="8">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="I20" s="6" t="s">
+      <c r="J20" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="8">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="M20" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="J20" s="6"/>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="21" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N20" s="6"/>
+      <c r="O20" s="8"/>
+    </row>
+    <row r="21" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1966,31 +2108,40 @@
         <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2002,31 +2153,40 @@
         <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="K22" s="1"/>
+      <c r="L22">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="M22" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2038,31 +2198,40 @@
         <v>68</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="M23" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="N23" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2074,31 +2243,40 @@
         <v>70</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G24" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2109,32 +2287,37 @@
       <c r="C25" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1"/>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="N25" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2145,32 +2328,37 @@
       <c r="C26" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="1"/>
+      <c r="E26" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="1"/>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I26" s="1" t="s">
+      <c r="J26" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="N26" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2181,32 +2369,39 @@
       <c r="C27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I27" s="1" t="s">
+      <c r="K27" s="1"/>
+      <c r="L27">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="N27" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2217,32 +2412,39 @@
       <c r="C28" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I28" s="1" t="s">
+      <c r="J28" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="K28" s="1"/>
+      <c r="L28">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2253,32 +2455,37 @@
       <c r="C29" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="1"/>
+      <c r="E29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="1"/>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="I29" s="1" t="s">
+      <c r="K29" s="1"/>
+      <c r="L29">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="M29" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2289,32 +2496,37 @@
       <c r="C30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="1"/>
+      <c r="E30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="1"/>
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I30" s="1" t="s">
+      <c r="K30" s="1"/>
+      <c r="L30">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="M30" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="N30" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2325,32 +2537,39 @@
       <c r="C31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="1"/>
+      <c r="E31" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I31" s="1" t="s">
+      <c r="K31" s="1"/>
+      <c r="L31">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="M31" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="N31" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2361,32 +2580,39 @@
       <c r="C32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="1"/>
+      <c r="E32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="G32" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="J32" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I32" s="1" t="s">
+      <c r="K32" s="1"/>
+      <c r="L32">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="M32" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="N32" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2398,27 +2624,36 @@
         <v>66</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1"/>
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="J33" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I33" s="1" t="s">
+      <c r="K33" s="1"/>
+      <c r="L33">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="M33" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J33" s="1"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N33" s="1"/>
+    </row>
+    <row r="34" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2430,27 +2665,36 @@
         <v>64</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1"/>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="J34" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I34" s="1" t="s">
+      <c r="K34" s="1"/>
+      <c r="L34">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="M34" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2461,26 +2705,35 @@
       <c r="C35" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="1"/>
+      <c r="E35" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I35" s="1" t="s">
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="M35" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J35" s="1"/>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2491,43 +2744,60 @@
       <c r="C36" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="6"/>
+      <c r="E36" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="G36" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="H36" s="8">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="J36" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H36" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I36" s="6" t="s">
+      <c r="K36" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="L36" s="8">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="M36" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="J36" s="6"/>
-      <c r="K36" s="5"/>
-    </row>
-    <row r="37" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N36" s="6"/>
+      <c r="O36" s="8"/>
+    </row>
+    <row r="37" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="1"/>
       <c r="C37" s="2"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="7" t="s">
+      <c r="E37" s="1"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="1"/>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="I37" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <f>A36+1</f>
         <v>32</v>
@@ -2535,21 +2805,26 @@
       <c r="B38" s="1"/>
       <c r="C38" s="2"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="1" t="s">
+      <c r="E38" s="1"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="1"/>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K38" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2557,21 +2832,24 @@
       <c r="B39" s="1"/>
       <c r="C39" s="2"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="1" t="s">
+      <c r="E39" s="1"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="1"/>
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J39" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2579,21 +2857,24 @@
       <c r="B40" s="1"/>
       <c r="C40" s="2"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="1" t="s">
+      <c r="E40" s="1"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="1"/>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J40" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="K40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2601,21 +2882,24 @@
       <c r="B41" s="1"/>
       <c r="C41" s="2"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="1" t="s">
+      <c r="E41" s="1"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="1"/>
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J41" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2623,21 +2907,26 @@
       <c r="B42" s="1"/>
       <c r="C42" s="2"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="1" t="s">
+      <c r="E42" s="1"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="1"/>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="J42" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H42" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K42" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2645,21 +2934,26 @@
       <c r="B43" s="1"/>
       <c r="C43" s="2"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="1" t="s">
+      <c r="E43" s="1"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="1"/>
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="J43" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K43" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2667,21 +2961,24 @@
       <c r="B44" s="1"/>
       <c r="C44" s="2"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="1" t="s">
+      <c r="E44" s="1"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="1"/>
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="2"/>
-    </row>
-    <row r="45" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J44" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="K44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+    </row>
+    <row r="45" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2689,21 +2986,24 @@
       <c r="B45" s="1"/>
       <c r="C45" s="2"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="1" t="s">
+      <c r="E45" s="1"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="1"/>
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J45" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="K45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+    </row>
+    <row r="46" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2711,21 +3011,24 @@
       <c r="B46" s="1"/>
       <c r="C46" s="2"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="1" t="s">
+      <c r="E46" s="1"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="1"/>
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="J46" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H46" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+    </row>
+    <row r="47" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2733,34 +3036,34 @@
       <c r="B47" s="1"/>
       <c r="C47" s="2"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="G47" s="1" t="s">
+      <c r="E47" s="1"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="1"/>
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H47" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="2"/>
+      <c r="J47" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="K47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J4:K59">
-    <sortCondition ref="K4:K59"/>
-  </sortState>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C5:C8 E7:E8 G9:G13 C33:C34 C16 G38 G35:G36 G42:G43 C12 C18:C24" numberStoredAsText="1"/>
+    <ignoredError sqref="C5:C8 F7:F8 J9:J13 C33:C34 C16 J38 J35:J36 J42:J43 C12 C18:C24" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/All-IOPins.xlsx
+++ b/All-IOPins.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sawtelles\Documents\GitHub\Teensy-Odd-and-Ends\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71831CA7-D14D-44F9-9788-4C7B3732D427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990A2674-8C32-4AA6-9395-73354780FB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="18240" windowHeight="28320" xr2:uid="{207FC95A-C154-4EA4-B2D9-D2F6000D8F44}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="284">
   <si>
     <t>BIT</t>
   </si>
@@ -879,6 +879,15 @@
   </si>
   <si>
     <t>TX1/MISO1</t>
+  </si>
+  <si>
+    <t>ETH_RST</t>
+  </si>
+  <si>
+    <t>ETH_INT</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
 </sst>
 </file>
@@ -916,7 +925,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -964,11 +973,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -996,6 +1067,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1331,26 +1412,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9656BE50-9C77-4DF8-ABEC-98B97523EA1E}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="6.85546875" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="6.88671875" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.88671875" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" customWidth="1"/>
     <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>205</v>
       </c>
@@ -1369,7 +1450,7 @@
       <c r="N1" s="12"/>
       <c r="O1" s="8"/>
     </row>
-    <row r="2" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>251</v>
       </c>
@@ -1388,7 +1469,7 @@
       <c r="N2" s="14"/>
       <c r="O2" s="9"/>
     </row>
-    <row r="3" spans="1:15" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>252</v>
       </c>
@@ -1407,7 +1488,7 @@
       <c r="N3" s="16"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1420,7 +1501,7 @@
       <c r="D4" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="17" t="s">
         <v>209</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -1429,7 +1510,7 @@
       <c r="G4" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="20" t="s">
         <v>0</v>
       </c>
       <c r="I4" s="4" t="s">
@@ -1454,7 +1535,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -1467,14 +1548,14 @@
       <c r="D5" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="18" t="s">
         <v>95</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G5" s="1"/>
-      <c r="H5">
+      <c r="H5" s="21">
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -1494,7 +1575,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>1</v>
@@ -1508,14 +1589,14 @@
       <c r="D6" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="18" t="s">
         <v>133</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>246</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6">
+      <c r="H6" s="21">
         <f>H5+1</f>
         <v>1</v>
       </c>
@@ -1537,7 +1618,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="7" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <f t="shared" ref="A7:A47" si="0">A6+1</f>
         <v>2</v>
@@ -1551,7 +1632,7 @@
       <c r="D7" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="18" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -1560,7 +1641,7 @@
       <c r="G7" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="21">
         <f t="shared" ref="H7:H47" si="1">H6+1</f>
         <v>2</v>
       </c>
@@ -1582,7 +1663,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="8" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1596,7 +1677,7 @@
       <c r="D8" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="18" t="s">
         <v>2</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -1605,7 +1686,7 @@
       <c r="G8" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="21">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -1627,7 +1708,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1639,14 +1720,14 @@
         <v>248</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="18" t="s">
         <v>134</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>173</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9">
+      <c r="H9" s="21">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -1668,7 +1749,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="10" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1680,14 +1761,14 @@
         <v>249</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="18" t="s">
         <v>135</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>172</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10">
+      <c r="H10" s="21">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -1709,7 +1790,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1721,14 +1802,14 @@
         <v>250</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="18" t="s">
         <v>136</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>174</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11">
+      <c r="H11" s="21">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1748,7 +1829,7 @@
       </c>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1756,18 +1837,15 @@
       <c r="B12" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C12" s="2">
-        <v>6</v>
-      </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="18" t="s">
         <v>137</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12">
+      <c r="H12" s="21">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -1787,7 +1865,7 @@
       </c>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1795,18 +1873,15 @@
       <c r="B13" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="18" t="s">
         <v>138</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>176</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="H13">
+      <c r="H13" s="21">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -1826,7 +1901,7 @@
       </c>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1838,14 +1913,14 @@
         <v>94</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="18" t="s">
         <v>139</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>177</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14">
+      <c r="H14" s="21">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -1865,7 +1940,7 @@
       </c>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1874,17 +1949,17 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>206</v>
+        <v>283</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="18" t="s">
         <v>140</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>178</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15">
+      <c r="H15" s="21">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -1904,7 +1979,7 @@
       </c>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1912,16 +1987,18 @@
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>208</v>
+      </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="18" t="s">
         <v>141</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>180</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16">
+      <c r="H16" s="21">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
@@ -1941,7 +2018,7 @@
       </c>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1953,7 +2030,7 @@
         <v>60</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="18" t="s">
         <v>45</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -1962,7 +2039,7 @@
       <c r="G17" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="21">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -1982,7 +2059,7 @@
       </c>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1990,9 +2067,11 @@
       <c r="B18" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="D18" s="1"/>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="18" t="s">
         <v>47</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -2001,7 +2080,7 @@
       <c r="G18" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="21">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
@@ -2021,7 +2100,7 @@
       </c>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2030,15 +2109,17 @@
         <v>148</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1" t="s">
+      <c r="D19" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>142</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>245</v>
       </c>
       <c r="G19" s="1"/>
-      <c r="H19">
+      <c r="H19" s="21">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
@@ -2058,7 +2139,7 @@
       </c>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2067,15 +2148,17 @@
         <v>149</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6" t="s">
+      <c r="D20" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="E20" s="19" t="s">
         <v>143</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>228</v>
       </c>
       <c r="G20" s="6"/>
-      <c r="H20" s="8">
+      <c r="H20" s="22">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -2096,7 +2179,7 @@
       <c r="N20" s="6"/>
       <c r="O20" s="8"/>
     </row>
-    <row r="21" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2110,7 +2193,7 @@
       <c r="D21" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="18" t="s">
         <v>35</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -2119,7 +2202,7 @@
       <c r="G21" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="21">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
@@ -2141,7 +2224,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2155,7 +2238,7 @@
       <c r="D22" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="18" t="s">
         <v>33</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -2164,7 +2247,7 @@
       <c r="G22" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="21">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
@@ -2186,7 +2269,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="23" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2200,7 +2283,7 @@
       <c r="D23" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="18" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -2209,7 +2292,7 @@
       <c r="G23" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="21">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
@@ -2231,7 +2314,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="24" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2245,7 +2328,7 @@
       <c r="D24" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -2254,7 +2337,7 @@
       <c r="G24" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="21">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
@@ -2276,7 +2359,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="25" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2288,14 +2371,14 @@
         <v>104</v>
       </c>
       <c r="D25" s="1"/>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="18" t="s">
         <v>77</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G25" s="1"/>
-      <c r="H25">
+      <c r="H25" s="21">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
@@ -2317,7 +2400,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="26" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2329,14 +2412,14 @@
         <v>104</v>
       </c>
       <c r="D26" s="1"/>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="18" t="s">
         <v>79</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G26" s="1"/>
-      <c r="H26">
+      <c r="H26" s="21">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -2358,7 +2441,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2370,7 +2453,7 @@
         <v>104</v>
       </c>
       <c r="D27" s="1"/>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="18" t="s">
         <v>31</v>
       </c>
       <c r="F27" s="2" t="s">
@@ -2379,7 +2462,7 @@
       <c r="G27" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="21">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
@@ -2401,7 +2484,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="28" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2413,7 +2496,7 @@
         <v>104</v>
       </c>
       <c r="D28" s="1"/>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="18" t="s">
         <v>29</v>
       </c>
       <c r="F28" s="2" t="s">
@@ -2422,7 +2505,7 @@
       <c r="G28" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="21">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
@@ -2444,7 +2527,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2456,14 +2539,14 @@
         <v>104</v>
       </c>
       <c r="D29" s="1"/>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="18" t="s">
         <v>41</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G29" s="1"/>
-      <c r="H29">
+      <c r="H29" s="21">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
@@ -2485,7 +2568,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="30" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2497,14 +2580,14 @@
         <v>104</v>
       </c>
       <c r="D30" s="1"/>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="18" t="s">
         <v>43</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G30" s="1"/>
-      <c r="H30">
+      <c r="H30" s="21">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
@@ -2526,7 +2609,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="31" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2538,7 +2621,7 @@
         <v>104</v>
       </c>
       <c r="D31" s="1"/>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="18" t="s">
         <v>37</v>
       </c>
       <c r="F31" s="2" t="s">
@@ -2547,7 +2630,7 @@
       <c r="G31" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="21">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
@@ -2569,7 +2652,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="32" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2581,7 +2664,7 @@
         <v>104</v>
       </c>
       <c r="D32" s="1"/>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="18" t="s">
         <v>39</v>
       </c>
       <c r="F32" s="2" t="s">
@@ -2590,7 +2673,7 @@
       <c r="G32" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="21">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
@@ -2612,7 +2695,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="33" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2626,14 +2709,14 @@
       <c r="D33" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="18" t="s">
         <v>73</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G33" s="1"/>
-      <c r="H33">
+      <c r="H33" s="21">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
@@ -2653,7 +2736,7 @@
       </c>
       <c r="N33" s="1"/>
     </row>
-    <row r="34" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2667,14 +2750,14 @@
       <c r="D34" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="18" t="s">
         <v>75</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G34" s="1"/>
-      <c r="H34">
+      <c r="H34" s="21">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
@@ -2694,7 +2777,7 @@
       </c>
       <c r="N34" s="1"/>
     </row>
-    <row r="35" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2706,7 +2789,7 @@
         <v>104</v>
       </c>
       <c r="D35" s="1"/>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="18" t="s">
         <v>49</v>
       </c>
       <c r="F35" s="2" t="s">
@@ -2715,7 +2798,7 @@
       <c r="G35" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="21">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
@@ -2733,7 +2816,7 @@
       </c>
       <c r="N35" s="1"/>
     </row>
-    <row r="36" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2745,7 +2828,7 @@
         <v>104</v>
       </c>
       <c r="D36" s="6"/>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="19" t="s">
         <v>51</v>
       </c>
       <c r="F36" s="5" t="s">
@@ -2754,7 +2837,7 @@
       <c r="G36" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="22">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
@@ -2777,15 +2860,15 @@
       <c r="N36" s="6"/>
       <c r="O36" s="8"/>
     </row>
-    <row r="37" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="1"/>
-      <c r="H37">
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="21">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
@@ -2797,18 +2880,18 @@
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
     </row>
-    <row r="38" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <f>A36+1</f>
         <v>32</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="1"/>
-      <c r="H38">
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="21">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
@@ -2824,18 +2907,18 @@
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
     </row>
-    <row r="39" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B39" s="1"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="1"/>
-      <c r="H39">
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="21">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
@@ -2849,18 +2932,18 @@
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
     </row>
-    <row r="40" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B40" s="1"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="1"/>
-      <c r="H40">
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="21">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
@@ -2874,18 +2957,18 @@
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
     </row>
-    <row r="41" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="1"/>
-      <c r="H41">
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="21">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
@@ -2899,18 +2982,18 @@
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
     </row>
-    <row r="42" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B42" s="1"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="1"/>
-      <c r="H42">
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="21">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
@@ -2926,18 +3009,18 @@
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B43" s="1"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="1"/>
-      <c r="H43">
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="21">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
@@ -2953,18 +3036,18 @@
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
     </row>
-    <row r="44" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B44" s="1"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="1"/>
-      <c r="H44">
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="21">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
@@ -2978,18 +3061,18 @@
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
     </row>
-    <row r="45" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B45" s="1"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="1"/>
-      <c r="H45">
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="21">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
@@ -3003,18 +3086,18 @@
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
     </row>
-    <row r="46" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B46" s="1"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="1"/>
-      <c r="H46">
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="21">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
@@ -3028,18 +3111,18 @@
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
     </row>
-    <row r="47" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B47" s="1"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="1"/>
-      <c r="H47">
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="21">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
@@ -3063,7 +3146,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C5:C8 F7:F8 J9:J13 C33:C34 C16 J38 J35:J36 J42:J43 C12 C18:C24" numberStoredAsText="1"/>
+    <ignoredError sqref="C5:C8 F7:F8 J9:J13 C33:C34 J38 J35:J36 J42:J43 C19:C24" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/All-IOPins.xlsx
+++ b/All-IOPins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sawtelles\Documents\GitHub\Teensy-Odd-and-Ends\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swsya\Documents\GitHub\Teensy-Odd-and-Ends\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71831CA7-D14D-44F9-9788-4C7B3732D427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C0D608-CE26-4D51-81C0-DD5CF5CCC3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="18240" windowHeight="28320" xr2:uid="{207FC95A-C154-4EA4-B2D9-D2F6000D8F44}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{207FC95A-C154-4EA4-B2D9-D2F6000D8F44}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -916,7 +916,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -964,11 +964,83 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -996,6 +1068,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1331,26 +1412,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9656BE50-9C77-4DF8-ABEC-98B97523EA1E}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="6.85546875" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="6.88671875" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.88671875" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" customWidth="1"/>
     <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>205</v>
       </c>
@@ -1369,7 +1450,7 @@
       <c r="N1" s="12"/>
       <c r="O1" s="8"/>
     </row>
-    <row r="2" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>251</v>
       </c>
@@ -1388,7 +1469,7 @@
       <c r="N2" s="14"/>
       <c r="O2" s="9"/>
     </row>
-    <row r="3" spans="1:15" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>252</v>
       </c>
@@ -1407,7 +1488,7 @@
       <c r="N3" s="16"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1417,7 +1498,7 @@
       <c r="C4" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="17" t="s">
         <v>275</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -1426,7 +1507,7 @@
       <c r="F4" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="17" t="s">
         <v>275</v>
       </c>
       <c r="H4" s="10" t="s">
@@ -1438,7 +1519,7 @@
       <c r="J4" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="20" t="s">
         <v>275</v>
       </c>
       <c r="L4" s="10" t="s">
@@ -1450,11 +1531,11 @@
       <c r="N4" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="23" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -1464,7 +1545,7 @@
       <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="18" t="s">
         <v>256</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -1473,7 +1554,7 @@
       <c r="F5" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="18"/>
       <c r="H5">
         <v>0</v>
       </c>
@@ -1483,7 +1564,7 @@
       <c r="J5" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K5" s="1"/>
+      <c r="K5" s="21"/>
       <c r="L5">
         <v>0</v>
       </c>
@@ -1493,8 +1574,9 @@
       <c r="N5" s="1" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O5" s="24"/>
+    </row>
+    <row r="6" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>1</v>
@@ -1505,7 +1587,7 @@
       <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="18" t="s">
         <v>253</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -1514,7 +1596,7 @@
       <c r="F6" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="18"/>
       <c r="H6">
         <f>H5+1</f>
         <v>1</v>
@@ -1525,7 +1607,7 @@
       <c r="J6" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="21"/>
       <c r="L6">
         <f>L5+1</f>
         <v>1</v>
@@ -1536,8 +1618,9 @@
       <c r="N6" s="1" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O6" s="24"/>
+    </row>
+    <row r="7" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <f t="shared" ref="A7:A47" si="0">A6+1</f>
         <v>2</v>
@@ -1548,7 +1631,7 @@
       <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="18" t="s">
         <v>254</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -1557,7 +1640,7 @@
       <c r="F7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="18" t="s">
         <v>280</v>
       </c>
       <c r="H7">
@@ -1570,7 +1653,7 @@
       <c r="J7" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="21"/>
       <c r="L7">
         <f t="shared" ref="L7:L36" si="2">L6+1</f>
         <v>2</v>
@@ -1581,8 +1664,9 @@
       <c r="N7" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O7" s="24"/>
+    </row>
+    <row r="8" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1593,7 +1677,7 @@
       <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="18" t="s">
         <v>255</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1602,7 +1686,7 @@
       <c r="F8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="18" t="s">
         <v>279</v>
       </c>
       <c r="H8">
@@ -1615,7 +1699,7 @@
       <c r="J8" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="21"/>
       <c r="L8">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -1626,8 +1710,9 @@
       <c r="N8" s="1" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O8" s="24"/>
+    </row>
+    <row r="9" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1638,14 +1723,14 @@
       <c r="C9" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="18"/>
       <c r="E9" s="1" t="s">
         <v>134</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="18"/>
       <c r="H9">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -1656,7 +1741,7 @@
       <c r="J9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="1"/>
+      <c r="K9" s="21"/>
       <c r="L9">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -1667,8 +1752,9 @@
       <c r="N9" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O9" s="24"/>
+    </row>
+    <row r="10" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1679,14 +1765,14 @@
       <c r="C10" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="18"/>
       <c r="H10">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -1697,7 +1783,7 @@
       <c r="J10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K10" s="1"/>
+      <c r="K10" s="21"/>
       <c r="L10">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -1708,8 +1794,9 @@
       <c r="N10" s="1" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="24"/>
+    </row>
+    <row r="11" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1720,14 +1807,14 @@
       <c r="C11" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="18"/>
       <c r="E11" s="1" t="s">
         <v>136</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="18"/>
       <c r="H11">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -1738,7 +1825,7 @@
       <c r="J11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="21"/>
       <c r="L11">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -1747,8 +1834,9 @@
         <v>107</v>
       </c>
       <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O11" s="24"/>
+    </row>
+    <row r="12" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1759,14 +1847,14 @@
       <c r="C12" s="2">
         <v>6</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="18"/>
       <c r="E12" s="1" t="s">
         <v>137</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="G12" s="18"/>
       <c r="H12">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -1777,7 +1865,7 @@
       <c r="J12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K12" s="1"/>
+      <c r="K12" s="21"/>
       <c r="L12">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -1786,8 +1874,9 @@
         <v>108</v>
       </c>
       <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O12" s="24"/>
+    </row>
+    <row r="13" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1798,14 +1887,14 @@
       <c r="C13" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D13" s="1"/>
+      <c r="D13" s="18"/>
       <c r="E13" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="G13" s="18"/>
       <c r="H13">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -1816,7 +1905,7 @@
       <c r="J13" s="1">
         <v>5</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="21"/>
       <c r="L13">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -1825,8 +1914,9 @@
         <v>109</v>
       </c>
       <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O13" s="24"/>
+    </row>
+    <row r="14" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1837,14 +1927,14 @@
       <c r="C14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="18"/>
       <c r="E14" s="1" t="s">
         <v>139</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" s="18"/>
       <c r="H14">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -1855,7 +1945,7 @@
       <c r="J14" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="K14" s="1"/>
+      <c r="K14" s="21"/>
       <c r="L14">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -1864,8 +1954,9 @@
         <v>110</v>
       </c>
       <c r="N14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O14" s="24"/>
+    </row>
+    <row r="15" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1876,14 +1967,14 @@
       <c r="C15" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="18"/>
       <c r="E15" s="1" t="s">
         <v>140</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="18"/>
       <c r="H15">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -1894,7 +1985,7 @@
       <c r="J15" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="K15" s="1"/>
+      <c r="K15" s="21"/>
       <c r="L15">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -1903,8 +1994,9 @@
         <v>111</v>
       </c>
       <c r="N15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O15" s="24"/>
+    </row>
+    <row r="16" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1913,14 +2005,14 @@
         <v>15</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="1"/>
+      <c r="D16" s="18"/>
       <c r="E16" s="1" t="s">
         <v>141</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G16" s="1"/>
+      <c r="G16" s="18"/>
       <c r="H16">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -1931,7 +2023,7 @@
       <c r="J16" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="K16" s="1"/>
+      <c r="K16" s="21"/>
       <c r="L16">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -1940,8 +2032,9 @@
         <v>112</v>
       </c>
       <c r="N16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O16" s="24"/>
+    </row>
+    <row r="17" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1952,14 +2045,14 @@
       <c r="C17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="18"/>
       <c r="E17" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="18" t="s">
         <v>273</v>
       </c>
       <c r="H17">
@@ -1972,7 +2065,7 @@
       <c r="J17" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K17" s="1"/>
+      <c r="K17" s="21"/>
       <c r="L17">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -1981,8 +2074,9 @@
         <v>113</v>
       </c>
       <c r="N17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O17" s="24"/>
+    </row>
+    <row r="18" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1991,14 +2085,14 @@
         <v>147</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="1"/>
+      <c r="D18" s="18"/>
       <c r="E18" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="18" t="s">
         <v>274</v>
       </c>
       <c r="H18">
@@ -2011,7 +2105,7 @@
       <c r="J18" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="K18" s="1"/>
+      <c r="K18" s="21"/>
       <c r="L18">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -2020,8 +2114,9 @@
         <v>114</v>
       </c>
       <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O18" s="24"/>
+    </row>
+    <row r="19" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2030,14 +2125,14 @@
         <v>148</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="1"/>
+      <c r="D19" s="18"/>
       <c r="E19" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="G19" s="18"/>
       <c r="H19">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -2048,7 +2143,7 @@
       <c r="J19" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="K19" s="1"/>
+      <c r="K19" s="21"/>
       <c r="L19">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -2057,8 +2152,9 @@
         <v>115</v>
       </c>
       <c r="N19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O19" s="24"/>
+    </row>
+    <row r="20" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2067,14 +2163,14 @@
         <v>149</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="6"/>
+      <c r="D20" s="19"/>
       <c r="E20" s="6" t="s">
         <v>143</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="G20" s="6"/>
+      <c r="G20" s="19"/>
       <c r="H20" s="8">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2085,7 +2181,7 @@
       <c r="J20" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="K20" s="6"/>
+      <c r="K20" s="22"/>
       <c r="L20" s="8">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -2094,9 +2190,9 @@
         <v>116</v>
       </c>
       <c r="N20" s="6"/>
-      <c r="O20" s="8"/>
-    </row>
-    <row r="21" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O20" s="25"/>
+    </row>
+    <row r="21" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2107,7 +2203,7 @@
       <c r="C21" s="2">
         <v>8</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="18" t="s">
         <v>257</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -2116,7 +2212,7 @@
       <c r="F21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="18" t="s">
         <v>269</v>
       </c>
       <c r="H21">
@@ -2129,7 +2225,7 @@
       <c r="J21" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K21" s="1"/>
+      <c r="K21" s="21"/>
       <c r="L21">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -2140,8 +2236,9 @@
       <c r="N21" s="1" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O21" s="24"/>
+    </row>
+    <row r="22" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2152,7 +2249,7 @@
       <c r="C22" s="2">
         <v>7</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="18" t="s">
         <v>258</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -2161,7 +2258,7 @@
       <c r="F22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="18" t="s">
         <v>270</v>
       </c>
       <c r="H22">
@@ -2174,7 +2271,7 @@
       <c r="J22" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="K22" s="1"/>
+      <c r="K22" s="21"/>
       <c r="L22">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -2185,8 +2282,9 @@
       <c r="N22" s="1" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O22" s="24"/>
+    </row>
+    <row r="23" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2197,7 +2295,7 @@
       <c r="C23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="18" t="s">
         <v>256</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -2206,7 +2304,7 @@
       <c r="F23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="18" t="s">
         <v>265</v>
       </c>
       <c r="H23">
@@ -2219,7 +2317,7 @@
       <c r="J23" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K23" s="1"/>
+      <c r="K23" s="21"/>
       <c r="L23">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -2230,8 +2328,9 @@
       <c r="N23" s="1" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O23" s="24"/>
+    </row>
+    <row r="24" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2242,7 +2341,7 @@
       <c r="C24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="18" t="s">
         <v>256</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -2251,7 +2350,7 @@
       <c r="F24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="18" t="s">
         <v>266</v>
       </c>
       <c r="H24">
@@ -2264,7 +2363,7 @@
       <c r="J24" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K24" s="1"/>
+      <c r="K24" s="21"/>
       <c r="L24">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -2275,8 +2374,9 @@
       <c r="N24" s="1" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O24" s="24"/>
+    </row>
+    <row r="25" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2287,14 +2387,14 @@
       <c r="C25" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="1"/>
+      <c r="D25" s="18"/>
       <c r="E25" s="1" t="s">
         <v>77</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G25" s="1"/>
+      <c r="G25" s="18"/>
       <c r="H25">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -2305,7 +2405,7 @@
       <c r="J25" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K25" s="1"/>
+      <c r="K25" s="21"/>
       <c r="L25">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -2316,8 +2416,9 @@
       <c r="N25" s="1" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O25" s="24"/>
+    </row>
+    <row r="26" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2328,14 +2429,14 @@
       <c r="C26" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="1"/>
+      <c r="D26" s="18"/>
       <c r="E26" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G26" s="1"/>
+      <c r="G26" s="18"/>
       <c r="H26">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -2346,7 +2447,7 @@
       <c r="J26" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K26" s="1"/>
+      <c r="K26" s="21"/>
       <c r="L26">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -2357,8 +2458,9 @@
       <c r="N26" s="1" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O26" s="24"/>
+    </row>
+    <row r="27" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2369,14 +2471,14 @@
       <c r="C27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="1"/>
+      <c r="D27" s="18"/>
       <c r="E27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="18" t="s">
         <v>271</v>
       </c>
       <c r="H27">
@@ -2389,7 +2491,7 @@
       <c r="J27" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K27" s="1"/>
+      <c r="K27" s="21"/>
       <c r="L27">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -2400,8 +2502,9 @@
       <c r="N27" s="1" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O27" s="24"/>
+    </row>
+    <row r="28" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2412,14 +2515,14 @@
       <c r="C28" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D28" s="1"/>
+      <c r="D28" s="18"/>
       <c r="E28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="18" t="s">
         <v>272</v>
       </c>
       <c r="H28">
@@ -2432,7 +2535,7 @@
       <c r="J28" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="K28" s="1"/>
+      <c r="K28" s="21"/>
       <c r="L28">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2443,8 +2546,9 @@
       <c r="N28" s="1" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O28" s="24"/>
+    </row>
+    <row r="29" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2455,14 +2559,14 @@
       <c r="C29" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="1"/>
+      <c r="D29" s="18"/>
       <c r="E29" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G29" s="1"/>
+      <c r="G29" s="18"/>
       <c r="H29">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -2473,7 +2577,7 @@
       <c r="J29" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="K29" s="1"/>
+      <c r="K29" s="21"/>
       <c r="L29">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -2484,8 +2588,9 @@
       <c r="N29" s="1" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O29" s="24"/>
+    </row>
+    <row r="30" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2496,14 +2601,14 @@
       <c r="C30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D30" s="1"/>
+      <c r="D30" s="18"/>
       <c r="E30" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="1"/>
+      <c r="G30" s="18"/>
       <c r="H30">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -2514,7 +2619,7 @@
       <c r="J30" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K30" s="1"/>
+      <c r="K30" s="21"/>
       <c r="L30">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -2525,8 +2630,9 @@
       <c r="N30" s="1" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O30" s="24"/>
+    </row>
+    <row r="31" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2537,14 +2643,14 @@
       <c r="C31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="1"/>
+      <c r="D31" s="18"/>
       <c r="E31" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="18" t="s">
         <v>267</v>
       </c>
       <c r="H31">
@@ -2557,7 +2663,7 @@
       <c r="J31" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="K31" s="1"/>
+      <c r="K31" s="21"/>
       <c r="L31">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -2568,8 +2674,9 @@
       <c r="N31" s="1" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O31" s="24"/>
+    </row>
+    <row r="32" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2580,14 +2687,14 @@
       <c r="C32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="1"/>
+      <c r="D32" s="18"/>
       <c r="E32" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="18" t="s">
         <v>268</v>
       </c>
       <c r="H32">
@@ -2600,7 +2707,7 @@
       <c r="J32" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="K32" s="1"/>
+      <c r="K32" s="21"/>
       <c r="L32">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -2611,8 +2718,9 @@
       <c r="N32" s="1" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O32" s="24"/>
+    </row>
+    <row r="33" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2623,7 +2731,7 @@
       <c r="C33" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="18" t="s">
         <v>259</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -2632,7 +2740,7 @@
       <c r="F33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G33" s="1"/>
+      <c r="G33" s="18"/>
       <c r="H33">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -2643,7 +2751,7 @@
       <c r="J33" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="K33" s="1"/>
+      <c r="K33" s="21"/>
       <c r="L33">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -2652,8 +2760,9 @@
         <v>129</v>
       </c>
       <c r="N33" s="1"/>
-    </row>
-    <row r="34" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O33" s="24"/>
+    </row>
+    <row r="34" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2664,7 +2773,7 @@
       <c r="C34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="18" t="s">
         <v>260</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -2673,7 +2782,7 @@
       <c r="F34" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G34" s="1"/>
+      <c r="G34" s="18"/>
       <c r="H34">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -2684,7 +2793,7 @@
       <c r="J34" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K34" s="1"/>
+      <c r="K34" s="21"/>
       <c r="L34">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -2693,8 +2802,9 @@
         <v>130</v>
       </c>
       <c r="N34" s="1"/>
-    </row>
-    <row r="35" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O34" s="24"/>
+    </row>
+    <row r="35" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2705,14 +2815,14 @@
       <c r="C35" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="1"/>
+      <c r="D35" s="18"/>
       <c r="E35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="18" t="s">
         <v>278</v>
       </c>
       <c r="H35">
@@ -2723,7 +2833,7 @@
         <v>164</v>
       </c>
       <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
+      <c r="K35" s="21"/>
       <c r="L35">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -2732,8 +2842,9 @@
         <v>131</v>
       </c>
       <c r="N35" s="1"/>
-    </row>
-    <row r="36" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O35" s="24"/>
+    </row>
+    <row r="36" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2744,14 +2855,14 @@
       <c r="C36" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="6"/>
+      <c r="D36" s="19"/>
       <c r="E36" s="6" t="s">
         <v>51</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="19" t="s">
         <v>277</v>
       </c>
       <c r="H36" s="8">
@@ -2764,7 +2875,7 @@
       <c r="J36" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="K36" s="22" t="s">
         <v>262</v>
       </c>
       <c r="L36" s="8">
@@ -2775,9 +2886,9 @@
         <v>132</v>
       </c>
       <c r="N36" s="6"/>
-      <c r="O36" s="8"/>
-    </row>
-    <row r="37" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O36" s="25"/>
+    </row>
+    <row r="37" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="1"/>
       <c r="C37" s="2"/>
@@ -2793,11 +2904,11 @@
         <v>211</v>
       </c>
       <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+      <c r="K37" s="21"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
     </row>
-    <row r="38" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <f>A36+1</f>
         <v>32</v>
@@ -2818,13 +2929,13 @@
       <c r="J38" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="K38" s="21" t="s">
         <v>261</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
     </row>
-    <row r="39" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2845,11 +2956,11 @@
       <c r="J39" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="K39" s="1"/>
+      <c r="K39" s="21"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
     </row>
-    <row r="40" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2870,11 +2981,11 @@
       <c r="J40" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="K40" s="1"/>
+      <c r="K40" s="21"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
     </row>
-    <row r="41" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2895,11 +3006,11 @@
       <c r="J41" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K41" s="1"/>
+      <c r="K41" s="21"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
     </row>
-    <row r="42" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2920,13 +3031,13 @@
       <c r="J42" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="K42" s="21" t="s">
         <v>264</v>
       </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2947,13 +3058,13 @@
       <c r="J43" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K43" s="21" t="s">
         <v>263</v>
       </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
     </row>
-    <row r="44" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2974,11 +3085,11 @@
       <c r="J44" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="K44" s="1"/>
+      <c r="K44" s="21"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
     </row>
-    <row r="45" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2999,11 +3110,11 @@
       <c r="J45" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="K45" s="1"/>
+      <c r="K45" s="21"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
     </row>
-    <row r="46" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3024,11 +3135,11 @@
       <c r="J46" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="K46" s="1"/>
+      <c r="K46" s="21"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
     </row>
-    <row r="47" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3049,7 +3160,7 @@
       <c r="J47" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="K47" s="1"/>
+      <c r="K47" s="21"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
     </row>

--- a/All-IOPins.xlsx
+++ b/All-IOPins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sawtelles\Documents\GitHub\Teensy-Odd-and-Ends\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990A2674-8C32-4AA6-9395-73354780FB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72299BC5-5AA1-4F98-86EB-E3423EE09A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="18240" windowHeight="28320" xr2:uid="{207FC95A-C154-4EA4-B2D9-D2F6000D8F44}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{207FC95A-C154-4EA4-B2D9-D2F6000D8F44}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="408">
   <si>
     <t>BIT</t>
   </si>
@@ -888,6 +888,378 @@
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>BALL</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>B9</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>E11</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>E12</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>B13</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>D13</t>
+  </si>
+  <si>
+    <t>D14</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>B14</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>E14</t>
+  </si>
+  <si>
+    <t>G14</t>
+  </si>
+  <si>
+    <t>J14</t>
+  </si>
+  <si>
+    <t>H14</t>
+  </si>
+  <si>
+    <t>K14</t>
+  </si>
+  <si>
+    <t>L14</t>
+  </si>
+  <si>
+    <t>F13</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>H10</t>
+  </si>
+  <si>
+    <t>L10</t>
+  </si>
+  <si>
+    <t>F14</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>G12</t>
+  </si>
+  <si>
+    <t>H13</t>
+  </si>
+  <si>
+    <t>H12</t>
+  </si>
+  <si>
+    <t>H11</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>L11</t>
+  </si>
+  <si>
+    <t>L12</t>
+  </si>
+  <si>
+    <t>L13</t>
+  </si>
+  <si>
+    <t>K11</t>
+  </si>
+  <si>
+    <t>K12</t>
+  </si>
+  <si>
+    <t>J11</t>
+  </si>
+  <si>
+    <t>J12</t>
+  </si>
+  <si>
+    <t>K10</t>
+  </si>
+  <si>
+    <t>H5</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>K1</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>B7</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>N4</t>
+  </si>
+  <si>
+    <t>N3</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>G11</t>
+  </si>
+  <si>
+    <t>J13</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1051,6 +1423,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1067,16 +1449,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1411,171 +1784,207 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9656BE50-9C77-4DF8-ABEC-98B97523EA1E}">
-  <dimension ref="A1:O47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S47"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" customWidth="1"/>
-    <col min="8" max="8" width="6.88671875" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="6.88671875" customWidth="1"/>
-    <col min="13" max="13" width="10.6640625" customWidth="1"/>
-    <col min="14" max="14" width="13.88671875" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="2" max="3" width="8.85546875" customWidth="1"/>
+    <col min="4" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="7" width="10.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" customWidth="1"/>
+    <col min="11" max="12" width="9.28515625" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="6.85546875" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="13.85546875" customWidth="1"/>
+    <col min="19" max="19" width="13" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="8"/>
-    </row>
-    <row r="2" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="8"/>
+    </row>
+    <row r="2" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="9"/>
-    </row>
-    <row r="3" spans="1:15" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="9"/>
+    </row>
+    <row r="3" spans="1:19" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="9"/>
-    </row>
-    <row r="4" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="9"/>
+    </row>
+    <row r="4" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="F4" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="J4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="L4" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="O4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="R4" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="S4" s="8" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="F5" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="21">
+      <c r="I5" s="1"/>
+      <c r="J5" s="15">
         <v>0</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="L5" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5">
+      <c r="N5" s="1"/>
+      <c r="O5">
         <v>0</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>1</v>
@@ -1583,42 +1992,54 @@
       <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="F6" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="27" t="s">
+        <v>331</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="21">
-        <f>H5+1</f>
+      <c r="I6" s="1"/>
+      <c r="J6" s="15">
+        <f>J5+1</f>
         <v>1</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="L6" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6">
-        <f>L5+1</f>
+      <c r="N6" s="1"/>
+      <c r="O6">
+        <f>O5+1</f>
         <v>1</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="7" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <f t="shared" ref="A7:A47" si="0">A6+1</f>
         <v>2</v>
@@ -1626,44 +2047,56 @@
       <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="F7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="H7" s="21">
-        <f t="shared" ref="H7:H47" si="1">H6+1</f>
+      <c r="J7" s="15">
+        <f t="shared" ref="J7:J47" si="1">J6+1</f>
         <v>2</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="L7" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="K7" s="1"/>
-      <c r="L7">
-        <f t="shared" ref="L7:L36" si="2">L6+1</f>
+      <c r="N7" s="1"/>
+      <c r="O7">
+        <f t="shared" ref="O7:O36" si="2">O6+1</f>
         <v>2</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="8" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1671,44 +2104,56 @@
       <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="F8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="27" t="s">
+        <v>406</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="H8" s="21">
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="L8" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="K8" s="1"/>
-      <c r="L8">
+      <c r="N8" s="1"/>
+      <c r="O8">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="Q8" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1716,40 +2161,52 @@
       <c r="B9" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="21">
+      <c r="I9" s="1"/>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="L9" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9">
+      <c r="N9" s="1"/>
+      <c r="O9">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="10" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1757,40 +2214,52 @@
       <c r="B10" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="27" t="s">
+        <v>322</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="21">
+      <c r="I10" s="1"/>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="L10" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K10" s="1"/>
-      <c r="L10">
+      <c r="N10" s="1"/>
+      <c r="O10">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1798,38 +2267,50 @@
       <c r="B11" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="21">
+      <c r="I11" s="1"/>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="L11" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="1"/>
-      <c r="L11">
+      <c r="N11" s="1"/>
+      <c r="O11">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="R11" s="1"/>
+    </row>
+    <row r="12" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1837,35 +2318,48 @@
       <c r="B12" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="18" t="s">
+      <c r="C12" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="21">
+      <c r="I12" s="1"/>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="L12" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="M12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K12" s="1"/>
-      <c r="L12">
+      <c r="N12" s="1"/>
+      <c r="O12">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="R12" s="1"/>
+    </row>
+    <row r="13" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1873,35 +2367,46 @@
       <c r="B13" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="18" t="s">
+      <c r="C13" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="21">
+      <c r="I13" s="1"/>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J13" s="1">
+      <c r="L13" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="M13" s="1">
         <v>5</v>
       </c>
-      <c r="K13" s="1"/>
-      <c r="L13">
+      <c r="N13" s="1"/>
+      <c r="O13">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+    </row>
+    <row r="14" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1909,38 +2414,48 @@
       <c r="B14" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="27" t="s">
+        <v>333</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="21">
+      <c r="I14" s="1"/>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="L14" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="K14" s="1"/>
-      <c r="L14">
+      <c r="N14" s="1"/>
+      <c r="O14">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="P14" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="N14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+    </row>
+    <row r="15" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1948,38 +2463,48 @@
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="1"/>
+      <c r="F15" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="27" t="s">
+        <v>322</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="21">
+      <c r="I15" s="1"/>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="L15" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="K15" s="1"/>
-      <c r="L15">
+      <c r="N15" s="1"/>
+      <c r="O15">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+    </row>
+    <row r="16" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1987,38 +2512,48 @@
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="1"/>
+      <c r="F16" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="21">
+      <c r="I16" s="1"/>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="L16" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="K16" s="1"/>
-      <c r="L16">
+      <c r="N16" s="1"/>
+      <c r="O16">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="N16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+    </row>
+    <row r="17" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2026,40 +2561,50 @@
       <c r="B17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="1"/>
+      <c r="F17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="H17" s="21">
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="L17" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K17" s="1"/>
-      <c r="L17">
+      <c r="N17" s="1"/>
+      <c r="O17">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="P17" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="N17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+    </row>
+    <row r="18" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2067,40 +2612,50 @@
       <c r="B18" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="1"/>
+      <c r="F18" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="27" t="s">
+        <v>326</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="H18" s="21">
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="L18" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="K18" s="1"/>
-      <c r="L18">
+      <c r="N18" s="1"/>
+      <c r="O18">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+    </row>
+    <row r="19" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2108,38 +2663,48 @@
       <c r="B19" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="F19" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="27" t="s">
+        <v>324</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="21">
+      <c r="I19" s="1"/>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="L19" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="K19" s="1"/>
-      <c r="L19">
+      <c r="N19" s="1"/>
+      <c r="O19">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="N19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+    </row>
+    <row r="20" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2147,39 +2712,49 @@
       <c r="B20" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="6" t="s">
+      <c r="C20" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="F20" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="22">
+      <c r="I20" s="6"/>
+      <c r="J20" s="16">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="K20" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="L20" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="M20" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="8">
+      <c r="N20" s="6"/>
+      <c r="O20" s="8">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="M20" s="6" t="s">
+      <c r="P20" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="N20" s="6"/>
-      <c r="O20" s="8"/>
-    </row>
-    <row r="21" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="8"/>
+    </row>
+    <row r="21" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2187,44 +2762,56 @@
       <c r="B21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D21" s="2">
         <v>8</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="F21" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="H21" s="21">
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="L21" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K21" s="1"/>
-      <c r="L21">
+      <c r="N21" s="1"/>
+      <c r="O21">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="P21" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="Q21" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2232,44 +2819,56 @@
       <c r="B22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D22" s="2">
         <v>7</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="F22" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H22" s="21">
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="L22" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="M22" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="K22" s="1"/>
-      <c r="L22">
+      <c r="N22" s="1"/>
+      <c r="O22">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="P22" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="Q22" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="23" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2277,44 +2876,56 @@
       <c r="B23" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="F23" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H23" s="21">
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="L23" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="M23" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K23" s="1"/>
-      <c r="L23">
+      <c r="N23" s="1"/>
+      <c r="O23">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="R23" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="24" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2322,44 +2933,56 @@
       <c r="B24" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="F24" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="H24" s="21">
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="L24" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K24" s="1"/>
-      <c r="L24">
+      <c r="N24" s="1"/>
+      <c r="O24">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="P24" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="Q24" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="25" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2367,40 +2990,52 @@
       <c r="B25" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="1"/>
+      <c r="F25" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="27" t="s">
+        <v>342</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="21">
+      <c r="I25" s="1"/>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="L25" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K25" s="1"/>
-      <c r="L25">
+      <c r="N25" s="1"/>
+      <c r="O25">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="P25" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="Q25" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="R25" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="26" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2408,40 +3043,52 @@
       <c r="B26" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="1"/>
+      <c r="F26" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="21">
+      <c r="I26" s="1"/>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="L26" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K26" s="1"/>
-      <c r="L26">
+      <c r="N26" s="1"/>
+      <c r="O26">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="P26" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="R26" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2449,42 +3096,54 @@
       <c r="B27" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="1"/>
+      <c r="F27" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" s="27" t="s">
+        <v>347</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="H27" s="21">
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="L27" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K27" s="1"/>
-      <c r="L27">
+      <c r="N27" s="1"/>
+      <c r="O27">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="P27" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="Q27" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="R27" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="28" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2492,42 +3151,54 @@
       <c r="B28" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="1"/>
+      <c r="F28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="H28" s="21">
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="L28" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="K28" s="1"/>
-      <c r="L28">
+      <c r="N28" s="1"/>
+      <c r="O28">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="Q28" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="R28" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2535,40 +3206,52 @@
       <c r="B29" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="1"/>
+      <c r="F29" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="21">
+      <c r="I29" s="1"/>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="K29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="L29" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="M29" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="K29" s="1"/>
-      <c r="L29">
+      <c r="N29" s="1"/>
+      <c r="O29">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="P29" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="Q29" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="R29" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="30" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2576,40 +3259,52 @@
       <c r="B30" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="1"/>
+      <c r="F30" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="21">
+      <c r="I30" s="1"/>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="L30" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="M30" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K30" s="1"/>
-      <c r="L30">
+      <c r="N30" s="1"/>
+      <c r="O30">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="R30" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="31" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2617,42 +3312,54 @@
       <c r="B31" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="1"/>
+      <c r="F31" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H31" s="21">
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="L31" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M31" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="K31" s="1"/>
-      <c r="L31">
+      <c r="N31" s="1"/>
+      <c r="O31">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="P31" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="Q31" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="R31" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="32" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2660,42 +3367,54 @@
       <c r="B32" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="1"/>
+      <c r="F32" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H32" s="21">
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="K32" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="L32" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M32" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="K32" s="1"/>
-      <c r="L32">
+      <c r="N32" s="1"/>
+      <c r="O32">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="P32" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="Q32" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="R32" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="33" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2703,40 +3422,50 @@
       <c r="B33" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="F33" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="G33" s="27" t="s">
+        <v>337</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="21">
+      <c r="I33" s="1"/>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="K33" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="L33" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="M33" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="K33" s="1"/>
-      <c r="L33">
+      <c r="N33" s="1"/>
+      <c r="O33">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="P33" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="N33" s="1"/>
-    </row>
-    <row r="34" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+    </row>
+    <row r="34" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2744,40 +3473,50 @@
       <c r="B34" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="F34" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="G34" s="27" t="s">
+        <v>338</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="21">
+      <c r="I34" s="1"/>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="K34" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="L34" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="M34" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K34" s="1"/>
-      <c r="L34">
+      <c r="N34" s="1"/>
+      <c r="O34">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="P34" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="N34" s="1"/>
-    </row>
-    <row r="35" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2785,38 +3524,48 @@
       <c r="B35" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="1"/>
+      <c r="F35" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="I35" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="H35" s="21">
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="K35" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35">
+      <c r="L35" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="P35" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="N35" s="1"/>
-    </row>
-    <row r="36" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+    </row>
+    <row r="36" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2824,329 +3573,403 @@
       <c r="B36" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="6"/>
+      <c r="F36" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="I36" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="H36" s="22">
+      <c r="J36" s="16">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="K36" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="J36" s="6" t="s">
+      <c r="L36" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="M36" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="N36" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="L36" s="8">
+      <c r="O36" s="8">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="M36" s="6" t="s">
+      <c r="P36" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="N36" s="6"/>
-      <c r="O36" s="8"/>
-    </row>
-    <row r="37" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="8"/>
+    </row>
+    <row r="37" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="21">
+      <c r="C37" s="1"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="K37" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+      <c r="L37" s="7"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
-    </row>
-    <row r="38" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <f>A36+1</f>
         <v>32</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="21">
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="L38" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="M38" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="N38" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-    </row>
-    <row r="39" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+    </row>
+    <row r="39" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B39" s="1"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="21">
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="K39" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="L39" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="M39" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="K39" s="1"/>
-      <c r="M39" s="1"/>
       <c r="N39" s="1"/>
-    </row>
-    <row r="40" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+    </row>
+    <row r="40" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B40" s="1"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="21">
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="K40" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="L40" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="M40" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="K40" s="1"/>
-      <c r="M40" s="1"/>
       <c r="N40" s="1"/>
-    </row>
-    <row r="41" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+    </row>
+    <row r="41" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="21">
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="L41" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="M41" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K41" s="1"/>
-      <c r="M41" s="1"/>
       <c r="N41" s="1"/>
-    </row>
-    <row r="42" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+    </row>
+    <row r="42" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B42" s="1"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="21">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="K42" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="L42" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="M42" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="N42" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-    </row>
-    <row r="43" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+    </row>
+    <row r="43" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B43" s="1"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="21">
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="K43" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="L43" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="M43" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="N43" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-    </row>
-    <row r="44" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+    </row>
+    <row r="44" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B44" s="1"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="26"/>
-      <c r="H44" s="21">
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="K44" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="L44" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="M44" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="K44" s="1"/>
-      <c r="M44" s="1"/>
       <c r="N44" s="1"/>
-    </row>
-    <row r="45" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+    </row>
+    <row r="45" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B45" s="1"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="21">
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="K45" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="L45" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="M45" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="K45" s="1"/>
-      <c r="M45" s="1"/>
       <c r="N45" s="1"/>
-    </row>
-    <row r="46" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+    </row>
+    <row r="46" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B46" s="1"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="21">
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="K46" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="L46" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="M46" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="K46" s="1"/>
-      <c r="M46" s="1"/>
       <c r="N46" s="1"/>
-    </row>
-    <row r="47" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+    </row>
+    <row r="47" spans="1:19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B47" s="1"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="21">
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="K47" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="L47" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="M47" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="K47" s="1"/>
-      <c r="M47" s="1"/>
       <c r="N47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A3:R3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C5:C8 F7:F8 J9:J13 C33:C34 J38 J35:J36 J42:J43 C19:C24" numberStoredAsText="1"/>
+    <ignoredError sqref="D5:D8 H7:H8 M9:M13 D33:D34 M38 M35:M36 M42:M43 D19:D24" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>